--- a/data/db/miniCRM/candidates_examples.xlsx
+++ b/data/db/miniCRM/candidates_examples.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medpersonal360-my.sharepoint.com/personal/tom_putilin_medpersonal360_com/Documents/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bcwgruppe-my.sharepoint.com/personal/528337_fom-net_de/Documents/Git/KI_unterstuetztes_BMS_v1/KI-unterstuetztes-BMS/data/db/miniCRM/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="23" documentId="11_08B2CF4D9AFB9C608E3EE0254893406FF894F0B0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B5CE9951-6564-487D-B9EE-29A8D377B089}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="212" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="212" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -69638,7 +69638,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.5" right="0.5" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="0" scale="0" orientation="portrait" usePrinterDefaults="0" useFirstPageNumber="1" horizontalDpi="0" verticalDpi="0" copies="0"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>

--- a/data/db/miniCRM/candidates_examples.xlsx
+++ b/data/db/miniCRM/candidates_examples.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bcwgruppe-my.sharepoint.com/personal/528337_fom-net_de/Documents/Git/KI_unterstuetztes_BMS_v1/KI-unterstuetztes-BMS/data/db/miniCRM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="11_08B2CF4D9AFB9C608E3EE0254893406FF894F0B0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B5CE9951-6564-487D-B9EE-29A8D377B089}"/>
+  <xr:revisionPtr revIDLastSave="35" documentId="11_08B2CF4D9AFB9C608E3EE0254893406FF894F0B0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8FD9AF6D-01D9-4261-95B6-2CB33AD80BF6}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="212" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="212" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$R$1246</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
@@ -18398,7 +18401,9 @@
   <dimension ref="A1:R1246"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="13" width="40" customWidth="1"/>
+    <col min="1" max="3" width="40" customWidth="1"/>
+    <col min="4" max="4" width="145.140625" customWidth="1"/>
+    <col min="5" max="13" width="40" customWidth="1"/>
     <col min="14" max="17" width="40" style="4" customWidth="1"/>
     <col min="18" max="18" width="40" customWidth="1"/>
   </cols>
@@ -65342,7 +65347,7 @@
       <c r="C1159" s="2" t="s">
         <v>2293</v>
       </c>
-      <c r="D1159" s="2" t="s">
+      <c r="D1159" s="5" t="s">
         <v>2294</v>
       </c>
       <c r="E1159" s="2" t="s">
@@ -66376,7 +66381,7 @@
       <c r="C1180" s="2" t="s">
         <v>2355</v>
       </c>
-      <c r="D1180" s="2" t="s">
+      <c r="D1180" s="5" t="s">
         <v>2356</v>
       </c>
       <c r="E1180" s="2" t="s">
@@ -68312,7 +68317,7 @@
       <c r="C1219" s="2" t="s">
         <v>2457</v>
       </c>
-      <c r="D1219" s="2" t="s">
+      <c r="D1219" s="5" t="s">
         <v>2458</v>
       </c>
       <c r="E1219" s="2" t="s">
@@ -69637,6 +69642,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:R1246" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.5" right="0.5" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" r:id="rId1"/>
   <headerFooter>

--- a/data/db/miniCRM/candidates_examples.xlsx
+++ b/data/db/miniCRM/candidates_examples.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bcwgruppe-my.sharepoint.com/personal/528337_fom-net_de/Documents/Git/KI_unterstuetztes_BMS_v1/KI-unterstuetztes-BMS/data/db/miniCRM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="35" documentId="11_08B2CF4D9AFB9C608E3EE0254893406FF894F0B0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8FD9AF6D-01D9-4261-95B6-2CB33AD80BF6}"/>
+  <xr:revisionPtr revIDLastSave="47" documentId="11_08B2CF4D9AFB9C608E3EE0254893406FF894F0B0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A79BF9F7-CA18-4F9E-8E91-6A3A82DF300E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="212" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18474,7 +18474,7 @@
       <c r="C2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="5" t="s">
         <v>21</v>
       </c>
       <c r="E2" s="2" t="s">
@@ -18526,7 +18526,7 @@
       <c r="C3" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="5" t="s">
         <v>32</v>
       </c>
       <c r="E3" s="2" t="s">
@@ -18582,7 +18582,7 @@
       <c r="C4" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="5" t="s">
         <v>41</v>
       </c>
       <c r="E4" s="2" t="s">
@@ -18634,7 +18634,7 @@
       <c r="C5" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="5" t="s">
         <v>48</v>
       </c>
       <c r="E5" s="2" t="s">
@@ -18688,7 +18688,7 @@
       <c r="C6" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="5" t="s">
         <v>52</v>
       </c>
       <c r="E6" s="2" t="s">
@@ -18740,7 +18740,7 @@
       <c r="C7" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="5" t="s">
         <v>59</v>
       </c>
       <c r="E7" s="2" t="s">
@@ -18964,7 +18964,7 @@
       <c r="C12" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="5" t="s">
         <v>79</v>
       </c>
       <c r="E12" s="2" t="s">
@@ -19248,7 +19248,7 @@
       <c r="C18" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="5" t="s">
         <v>103</v>
       </c>
       <c r="E18" s="2" t="s">
@@ -19460,7 +19460,7 @@
         <v>66</v>
       </c>
       <c r="C22" s="2"/>
-      <c r="D22" s="2" t="s">
+      <c r="D22" s="5" t="s">
         <v>125</v>
       </c>
       <c r="E22" s="2" t="s">
@@ -19730,7 +19730,7 @@
       <c r="C29" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="D29" s="5" t="s">
         <v>142</v>
       </c>
       <c r="E29" s="2" t="s">
@@ -19806,7 +19806,7 @@
         <v>66</v>
       </c>
       <c r="C31" s="2"/>
-      <c r="D31" s="2" t="s">
+      <c r="D31" s="5" t="s">
         <v>149</v>
       </c>
       <c r="E31" s="2" t="s">
@@ -20113,7 +20113,7 @@
       <c r="B39" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" s="5" t="s">
         <v>162</v>
       </c>
       <c r="D39" s="2"/>
